--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_attackmode_ext_info[攻击模块扩展信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_attackmode_ext_info[攻击模块扩展信息].xlsx
@@ -1038,7 +1038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="38.25" customWidth="1" style="1" min="2" max="4"/>
@@ -1184,26 +1184,62 @@
       </c>
     </row>
     <row r="7" ht="15" customHeight="1" s="1">
-      <c r="A7" t="n">
+      <c r="A7" s="0" t="n">
         <v>100004</v>
       </c>
-      <c r="B7" t="n">
+      <c r="B7" s="0" t="n">
         <v>102002</v>
       </c>
-      <c r="C7" t="n">
+      <c r="C7" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="D7" t="n">
+      <c r="D7" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E7" s="0" t="inlineStr">
         <is>
           <t>向前挥砍,攻击前方上中下三排单位</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" s="1"/>
-    <row r="9" ht="15" customHeight="1" s="1"/>
+    <row r="8" ht="15" customHeight="1" s="1">
+      <c r="A8" s="0" t="n">
+        <v>100006</v>
+      </c>
+      <c r="B8" s="0" t="n">
+        <v>700005</v>
+      </c>
+      <c r="C8" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="E8" s="0" t="inlineStr">
+        <is>
+          <t>BOSS技能-冰大魔法师-天降冰球(随机落点,5秒一次)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1" s="1">
+      <c r="A9" s="0" t="n">
+        <v>100007</v>
+      </c>
+      <c r="B9" s="0" t="n">
+        <v>700006</v>
+      </c>
+      <c r="C9" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="E9" s="0" t="inlineStr">
+        <is>
+          <t>BOSS技能-雷大魔法师-天降雷电(随机落点,5秒一次)</t>
+        </is>
+      </c>
+    </row>
     <row r="10" ht="15" customHeight="1" s="1"/>
     <row r="11" ht="15" customHeight="1" s="1"/>
     <row r="43" ht="12" customHeight="1" s="1"/>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_attackmode_ext_info[攻击模块扩展信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_attackmode_ext_info[攻击模块扩展信息].xlsx
@@ -1038,7 +1038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="38.25" customWidth="1" style="1" min="2" max="4"/>
@@ -1066,7 +1066,12 @@
           <t>trigger_interval</t>
         </is>
       </c>
-      <c r="E1" s="0" t="inlineStr">
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>trigger_scene</t>
+        </is>
+      </c>
+      <c r="F1" s="0" t="inlineStr">
         <is>
           <t>remark</t>
         </is>
@@ -1093,7 +1098,12 @@
           <t>float</t>
         </is>
       </c>
-      <c r="E2" s="0" t="inlineStr">
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="F2" s="0" t="inlineStr">
         <is>
           <t>string</t>
         </is>
@@ -1120,7 +1130,12 @@
           <t>释放间隔（秒）</t>
         </is>
       </c>
-      <c r="E3" s="0" t="inlineStr">
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>触发场景(默认0): 0=攻击意图内释放(攻击循环出手点,trigger_interval生效); 1=释放技能意图(由NPC ai_param的skill_update事件全局周期驱动,走路也放,trigger_interval无效以ai_param为准)</t>
+        </is>
+      </c>
+      <c r="F3" s="0" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
@@ -1139,7 +1154,7 @@
       <c r="D4" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="E4" s="0" t="inlineStr">
+      <c r="F4" s="0" t="inlineStr">
         <is>
           <t>向前挥砍，攻击前方一排单位</t>
         </is>
@@ -1158,7 +1173,7 @@
       <c r="D5" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="E5" s="0" t="inlineStr">
+      <c r="F5" s="0" t="inlineStr">
         <is>
           <t>BOSS技能-火大魔法师-天降陨石(随机落点,5秒一次)</t>
         </is>
@@ -1177,7 +1192,7 @@
       <c r="D6" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="E6" s="0" t="inlineStr">
+      <c r="F6" s="0" t="inlineStr">
         <is>
           <t>BOSS技能-水大魔法师-天降水滴(随机落点,5秒一次)</t>
         </is>
@@ -1196,7 +1211,7 @@
       <c r="D7" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="E7" s="0" t="inlineStr">
+      <c r="F7" s="0" t="inlineStr">
         <is>
           <t>向前挥砍,攻击前方上中下三排单位</t>
         </is>
@@ -1204,29 +1219,32 @@
     </row>
     <row r="8" ht="15" customHeight="1" s="1">
       <c r="A8" s="0" t="n">
-        <v>100006</v>
+        <v>100005</v>
       </c>
       <c r="B8" s="0" t="n">
-        <v>700005</v>
+        <v>500003</v>
       </c>
       <c r="C8" s="0" t="n">
         <v>1</v>
       </c>
       <c r="D8" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="E8" s="0" t="inlineStr">
-        <is>
-          <t>BOSS技能-冰大魔法师-天降冰球(随机落点,5秒一次)</t>
+        <v>10</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" s="0" t="inlineStr">
+        <is>
+          <t>BOSS全局技能-大盾战士-援护护盾(给最前排3个友军套伤害转移护盾,固定10秒一次,走路也放)</t>
         </is>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1" s="1">
       <c r="A9" s="0" t="n">
-        <v>100007</v>
+        <v>100006</v>
       </c>
       <c r="B9" s="0" t="n">
-        <v>700006</v>
+        <v>700005</v>
       </c>
       <c r="C9" s="0" t="n">
         <v>1</v>
@@ -1234,13 +1252,31 @@
       <c r="D9" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="E9" s="0" t="inlineStr">
+      <c r="F9" s="0" t="inlineStr">
+        <is>
+          <t>BOSS技能-冰大魔法师-天降冰球(随机落点,5秒一次)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1" s="1">
+      <c r="A10" s="0" t="n">
+        <v>100007</v>
+      </c>
+      <c r="B10" s="0" t="n">
+        <v>700006</v>
+      </c>
+      <c r="C10" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="F10" s="0" t="inlineStr">
         <is>
           <t>BOSS技能-雷大魔法师-天降雷电(随机落点,5秒一次)</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1" s="1"/>
     <row r="11" ht="15" customHeight="1" s="1"/>
     <row r="43" ht="12" customHeight="1" s="1"/>
     <row r="44" ht="12" customHeight="1" s="1"/>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_attackmode_ext_info[攻击模块扩展信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_attackmode_ext_info[攻击模块扩展信息].xlsx
@@ -1066,7 +1066,7 @@
           <t>trigger_interval</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="0" t="inlineStr">
         <is>
           <t>trigger_scene</t>
         </is>
@@ -1098,7 +1098,7 @@
           <t>float</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" s="0" t="inlineStr">
         <is>
           <t>int</t>
         </is>
@@ -1130,7 +1130,7 @@
           <t>释放间隔（秒）</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" s="0" t="inlineStr">
         <is>
           <t>触发场景(默认0): 0=攻击意图内释放(攻击循环出手点,trigger_interval生效); 1=释放技能意图(由NPC ai_param的skill_update事件全局周期驱动,走路也放,trigger_interval无效以ai_param为准)</t>
         </is>
@@ -1230,7 +1230,7 @@
       <c r="D8" s="0" t="n">
         <v>10</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8" s="0" t="n">
         <v>1</v>
       </c>
       <c r="F8" s="0" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="F10" s="0" t="inlineStr">
         <is>
-          <t>BOSS技能-雷大魔法师-天降雷电(随机落点,5秒一次)</t>
+          <t>BOSS技能-雷大魔法师-三连雷击(0.5秒3发完整普攻雷击,独立随机落点,5秒一次)</t>
         </is>
       </c>
     </row>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_attackmode_ext_info[攻击模块扩展信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_attackmode_ext_info[攻击模块扩展信息].xlsx
@@ -1273,7 +1273,7 @@
       </c>
       <c r="F10" s="0" t="inlineStr">
         <is>
-          <t>BOSS技能-雷大魔法师-三连雷击(0.5秒3发完整普攻雷击,独立随机落点,5秒一次)</t>
+          <t>BOSS技能-雷大魔法师-三连雷击(0.5秒3发800002BOSS雷击[特效Effect_Thunder_4],独立随机落点,5秒一次)</t>
         </is>
       </c>
     </row>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_attackmode_ext_info[攻击模块扩展信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_attackmode_ext_info[攻击模块扩展信息].xlsx
@@ -1038,7 +1038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="38.25" customWidth="1" style="1" min="2" max="4"/>
@@ -1277,7 +1277,25 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1" s="1"/>
+    <row r="11" ht="15" customHeight="1" s="1">
+      <c r="A11" s="0" t="n">
+        <v>100008</v>
+      </c>
+      <c r="B11" s="0" t="n">
+        <v>500005</v>
+      </c>
+      <c r="C11" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" s="0" t="n">
+        <v>30</v>
+      </c>
+      <c r="F11" s="0" t="inlineStr">
+        <is>
+          <t>BOSS技能-骷髅召唤师-三路召唤（自己所在路+上下相邻路每路3只骷髅，30秒一发顶替当次普攻）</t>
+        </is>
+      </c>
+    </row>
     <row r="43" ht="12" customHeight="1" s="1"/>
     <row r="44" ht="12" customHeight="1" s="1"/>
     <row r="45" ht="12" customHeight="1" s="1"/>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_attackmode_ext_info[攻击模块扩展信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_attackmode_ext_info[攻击模块扩展信息].xlsx
@@ -1038,7 +1038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="38.25" customWidth="1" style="1" min="2" max="4"/>
@@ -1293,6 +1293,50 @@
       <c r="F11" s="0" t="inlineStr">
         <is>
           <t>BOSS技能-骷髅召唤师-三路召唤（自己所在路+上下相邻路每路3只骷髅，30秒一发顶替当次普攻）</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="0" t="n">
+        <v>100009</v>
+      </c>
+      <c r="B12" s="0" t="n">
+        <v>500006</v>
+      </c>
+      <c r="C12" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E12" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" s="0" t="inlineStr">
+        <is>
+          <t>全局技能-牧师-群体治疗(自身周围5格治疗HP不满友军=ATK,固定3秒一次,走路也放)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>100010</v>
+      </c>
+      <c r="B13" t="n">
+        <v>500007</v>
+      </c>
+      <c r="C13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" t="n">
+        <v>10</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>BOSS全局技能-神官-地面持续治疗(半径2区域5秒每秒回血ATK×0.1,固定10秒一次,走路也放)</t>
         </is>
       </c>
     </row>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_attackmode_ext_info[攻击模块扩展信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_attackmode_ext_info[攻击模块扩展信息].xlsx
@@ -1038,7 +1038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="38.25" customWidth="1" style="1" min="2" max="4"/>
@@ -1132,7 +1132,7 @@
       </c>
       <c r="E3" s="0" t="inlineStr">
         <is>
-          <t>触发场景(默认0): 0=攻击意图内释放(攻击循环出手点,trigger_interval生效); 1=释放技能意图(由NPC ai_param的skill_update事件全局周期驱动,走路也放,trigger_interval无效以ai_param为准)</t>
+          <t>触发场景(默认0): 0=攻击意图内释放(攻击循环出手点,trigger_interval生效); 1=释放技能意图(由NPC ai_param的skill_update事件全局周期驱动,走路也放,trigger_interval无效以ai_param为准); 2=替代普攻(攻击意图内每次出手随机选取一个顶替普攻,无CD,trigger_interval失效)</t>
         </is>
       </c>
       <c r="F3" s="0" t="inlineStr">
@@ -1319,24 +1319,112 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="n">
+      <c r="A13" s="0" t="n">
         <v>100010</v>
       </c>
-      <c r="B13" t="n">
+      <c r="B13" s="0" t="n">
         <v>500007</v>
       </c>
-      <c r="C13" t="n">
-        <v>1</v>
-      </c>
-      <c r="D13" t="n">
+      <c r="C13" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" s="0" t="n">
         <v>10</v>
       </c>
-      <c r="E13" t="n">
-        <v>1</v>
-      </c>
-      <c r="F13" t="inlineStr">
+      <c r="E13" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" s="0" t="inlineStr">
         <is>
           <t>BOSS全局技能-神官-地面持续治疗(半径2区域5秒每秒回血ATK×0.1,固定10秒一次,走路也放)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>100011</v>
+      </c>
+      <c r="B14" t="n">
+        <v>700001</v>
+      </c>
+      <c r="C14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="n">
+        <v>2</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>BOSS技能-大魔导师-天降陨石(替代普攻,每次出手随机四系之一,trigger_interval失效)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>100012</v>
+      </c>
+      <c r="B15" t="n">
+        <v>700002</v>
+      </c>
+      <c r="C15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="n">
+        <v>2</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>BOSS技能-大魔导师-天降水滴(替代普攻,每次出手随机四系之一,trigger_interval失效)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>100013</v>
+      </c>
+      <c r="B16" t="n">
+        <v>700005</v>
+      </c>
+      <c r="C16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="n">
+        <v>2</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>BOSS技能-大魔导师-天降冰球(替代普攻,每次出手随机四系之一,trigger_interval失效)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>100014</v>
+      </c>
+      <c r="B17" t="n">
+        <v>700006</v>
+      </c>
+      <c r="C17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="n">
+        <v>2</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>BOSS技能-大魔导师-三连雷击(替代普攻,每次出手随机四系之一,trigger_interval失效)</t>
         </is>
       </c>
     </row>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_attackmode_ext_info[攻击模块扩展信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_attackmode_ext_info[攻击模块扩展信息].xlsx
@@ -1235,7 +1235,7 @@
       </c>
       <c r="F8" s="0" t="inlineStr">
         <is>
-          <t>BOSS全局技能-大盾战士-援护护盾(给最前排3个友军套伤害转移护盾,固定10秒一次,走路也放)</t>
+          <t>BOSS全局技能-大盾战士-援护护盾(给1个最前排+其余随机友军套伤害转移护盾,固定10秒一次,走路也放)</t>
         </is>
       </c>
     </row>
@@ -1341,88 +1341,88 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="n">
+      <c r="A14" s="0" t="n">
         <v>100011</v>
       </c>
-      <c r="B14" t="n">
+      <c r="B14" s="0" t="n">
         <v>700001</v>
       </c>
-      <c r="C14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D14" t="n">
+      <c r="C14" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="E14" t="n">
+      <c r="E14" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F14" s="0" t="inlineStr">
         <is>
           <t>BOSS技能-大魔导师-天降陨石(替代普攻,每次出手随机四系之一,trigger_interval失效)</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="n">
+      <c r="A15" s="0" t="n">
         <v>100012</v>
       </c>
-      <c r="B15" t="n">
+      <c r="B15" s="0" t="n">
         <v>700002</v>
       </c>
-      <c r="C15" t="n">
-        <v>1</v>
-      </c>
-      <c r="D15" t="n">
+      <c r="C15" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="E15" t="n">
+      <c r="E15" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F15" s="0" t="inlineStr">
         <is>
           <t>BOSS技能-大魔导师-天降水滴(替代普攻,每次出手随机四系之一,trigger_interval失效)</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="n">
+      <c r="A16" s="0" t="n">
         <v>100013</v>
       </c>
-      <c r="B16" t="n">
+      <c r="B16" s="0" t="n">
         <v>700005</v>
       </c>
-      <c r="C16" t="n">
-        <v>1</v>
-      </c>
-      <c r="D16" t="n">
+      <c r="C16" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="E16" t="n">
+      <c r="E16" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F16" s="0" t="inlineStr">
         <is>
           <t>BOSS技能-大魔导师-天降冰球(替代普攻,每次出手随机四系之一,trigger_interval失效)</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="n">
+      <c r="A17" s="0" t="n">
         <v>100014</v>
       </c>
-      <c r="B17" t="n">
+      <c r="B17" s="0" t="n">
         <v>700006</v>
       </c>
-      <c r="C17" t="n">
-        <v>1</v>
-      </c>
-      <c r="D17" t="n">
+      <c r="C17" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="E17" t="n">
+      <c r="E17" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F17" s="0" t="inlineStr">
         <is>
           <t>BOSS技能-大魔导师-三连雷击(替代普攻,每次出手随机四系之一,trigger_interval失效)</t>
         </is>
